--- a/jogos_2024-10-28.xlsx
+++ b/jogos_2024-10-28.xlsx
@@ -1794,35 +1794,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>7.41</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.1</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.95</v>
+        <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.39</v>
+        <v>1.61</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['22', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45593.5</v>
@@ -1923,35 +1923,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enugu Rangers</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.57</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AA12" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.72</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.33</v>
+        <v>1.49</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45593.5</v>
@@ -2052,35 +2052,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>7.41</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.16</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
-        <v>4.57</v>
+        <v>2.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.49</v>
+        <v>3.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.61</v>
+        <v>2.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '57']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45593.5</v>
@@ -2181,35 +2181,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Enugu Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.62</v>
+        <v>5.75</v>
       </c>
       <c r="O14" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X14" t="n">
         <v>2.25</v>
       </c>
-      <c r="R14" t="n">
+      <c r="Y14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.44</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA14" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.49</v>
+        <v>4.33</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45593.5</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.89</v>
+        <v>4.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.89</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>3.34</v>
+        <v>2.32</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.98</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['42', '49']</t>
+          <t>['4', '68', '90+3']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45593.52083333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.75</v>
+        <v>3.89</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.89</v>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="U16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.25</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.55</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.32</v>
+        <v>3.34</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['4', '68', '90+3']</t>
+          <t>['42', '49']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.65</v>
+        <v>1.97</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45593.52083333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>2.11</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>4.63</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['8', '15']</t>
+          <t>['13', '67']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['22', '27', '46']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>2.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45593.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,28 +3120,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>2.63</v>
@@ -3150,53 +3150,53 @@
         <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '15']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['22', '27', '46']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>2.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.96</v>
+        <v>1.12</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45593.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['13', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45593.58333333334</v>
@@ -3471,119 +3471,119 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="Y24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['30', '48']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.19</v>
       </c>
-      <c r="X24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['11', '33', '75', '79']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45593.625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,103 +3610,103 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O25" t="n">
         <v>3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.88</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA25" t="n">
         <v>3.6</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['7', '35', '84']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AI25" t="n">
         <v>1.73</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.6</v>
       </c>
-      <c r="N26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.75</v>
-      </c>
       <c r="P26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['11', '33', '75', '79']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['48', '82', '86']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45593.625</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>5.12</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.72</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['34', '47']</t>
+          <t>['40', '50']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['36', '56', '90+2']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>2.55</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45593.625</v>
@@ -3987,119 +3987,119 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skövde AIK</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.33</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['34', '47']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.44</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['50', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['27', '72']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AI28" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.05</v>
+        <v>1.83</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45593.625</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Skövde AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="M29" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.12</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.25</v>
       </c>
-      <c r="S29" t="n">
+      <c r="X29" t="n">
         <v>3.75</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X29" t="n">
-        <v>5.5</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['40', '50']</t>
+          <t>['50', '90+4']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['36', '56', '90+2']</t>
+          <t>['27', '72']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45593.625</v>
@@ -4245,119 +4245,119 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>4.11</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.82</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U30" t="n">
         <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['30', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['7', '35', '84']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45593.625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,16 +4384,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['48', '82', '86']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2.75</v>
       </c>
-      <c r="O31" t="n">
-        <v>3</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45593.625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U34" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X34" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['6', '12', '59']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['52', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['74', '88']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45593.66666666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O35" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="T35" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X35" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['6', '12', '59']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['52', '90+5']</t>
+          <t>['74', '88']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45593.66666666666</v>
@@ -5793,35 +5793,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O42" t="n">
         <v>5</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O42" t="n">
-        <v>5.5</v>
-      </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC42" t="n">
         <v>2.2</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD42" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['18', '52']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45593.79166666666</v>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S44" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="U44" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V44" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X44" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['18', '52']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45593.79166666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
         <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="X47" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['12', '18', '32']</t>
+          <t>['9', '65']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['42', '75']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45593.875</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
         <v>2</v>
       </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="M49" t="n">
         <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T49" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="X49" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['9', '65']</t>
+          <t>['12', '18', '32']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['42', '75']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45593.875</v>
